--- a/3/C6/vv/Practicas/Practica5/pruebas-kata-Gilded-Rose.xlsx
+++ b/3/C6/vv/Practicas/Practica5/pruebas-kata-Gilded-Rose.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Docencia\Verificación y Validación\practicas\p5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imadx\Documents\GitHub\PracticasConBellido\3\C6\vv\Practicas\Practica5\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B51F13E-F318-4515-AED7-1396CFA3BA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9330"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
   <si>
     <t>Prueba</t>
   </si>
@@ -207,13 +208,61 @@
   </si>
   <si>
     <t>Test en InventoryTest</t>
+  </si>
+  <si>
+    <t>should_never_changes_sellIn_of_Sulfuras</t>
+  </si>
+  <si>
+    <t>should_lower_the_sellIn_by_one_for_normal_items</t>
+  </si>
+  <si>
+    <t>should_lower_the_quality_by_one_for_normal_items</t>
+  </si>
+  <si>
+    <t>should_not_lower_the_quality_below_zero</t>
+  </si>
+  <si>
+    <t>should_lower_the_quality_twice_as_fast_once_the_sell_in_date_has_passed</t>
+  </si>
+  <si>
+    <t>should_increase_the_quality_of_aged_brie_as_it_gets_older</t>
+  </si>
+  <si>
+    <t>should_not_increase_the_quality_of_aged_brie_over_50</t>
+  </si>
+  <si>
+    <t>should_lower_backstage_passes_to_zero_quality_once_concert_has_happened</t>
+  </si>
+  <si>
+    <t>should_increase_backstage_passes_quality_by_1_when_the_concert_is_more_than_10_days_away</t>
+  </si>
+  <si>
+    <t>should_increase_backstage_passes_quality_by_2_when_the_concert_is_10_days_or_less_away</t>
+  </si>
+  <si>
+    <t>should_increase_backstage_passes_quality_by_3_when_the_concert_is_5_days_or_less_away</t>
+  </si>
+  <si>
+    <t>should_not_increase_backstage_passes_above_a_quality_of_50</t>
+  </si>
+  <si>
+    <t>should_increase_the_quality_of_aged_brie_twice_as_fast_once_the_sell_in_date_has_passed</t>
+  </si>
+  <si>
+    <t>should_not_lower_the_quality_below_zero_when_expired</t>
+  </si>
+  <si>
+    <t>should_not_increase_the_quality_of_aged_brie_over_50_when_expired</t>
+  </si>
+  <si>
+    <t>should_never_changes_quailty_of_Sulfuras/should_never_changes_quailty_of_Sulfuras_when_expired</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -648,7 +697,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -714,9 +763,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -747,6 +793,51 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -765,15 +856,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,42 +863,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1064,45 +1110,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="5.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="2" customWidth="1"/>
-    <col min="11" max="12" width="50.7109375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5703125" style="2"/>
+    <col min="2" max="2" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="5.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="44.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="86" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="62" t="s">
+      <c r="I1" s="51" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="57"/>
@@ -1111,14 +1158,14 @@
       </c>
       <c r="L1" s="57"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
+    <row r="2" spans="1:12" ht="15" thickBot="1">
+      <c r="A2" s="48"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
       <c r="H2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1135,7 +1182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1167,9 +1214,11 @@
         <v>26</v>
       </c>
       <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1182,11 +1231,11 @@
       <c r="D4" s="17">
         <v>50</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
       <c r="H4" s="18"/>
       <c r="I4" s="17">
         <v>9</v>
@@ -1195,9 +1244,11 @@
         <v>50</v>
       </c>
       <c r="K4" s="14"/>
-      <c r="L4" s="15"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
         <v>12</v>
       </c>
@@ -1231,7 +1282,7 @@
       <c r="K5" s="27"/>
       <c r="L5" s="28"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="20" t="s">
         <v>14</v>
       </c>
@@ -1244,11 +1295,11 @@
       <c r="D6" s="22">
         <v>50</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="55"/>
       <c r="H6" s="25"/>
       <c r="I6" s="22">
         <v>-9</v>
@@ -1257,9 +1308,11 @@
         <v>50</v>
       </c>
       <c r="K6" s="27"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
         <v>15</v>
       </c>
@@ -1272,11 +1325,11 @@
       <c r="D7" s="22">
         <v>49</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="51"/>
-      <c r="G7" s="52"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="55"/>
       <c r="H7" s="25"/>
       <c r="I7" s="22">
         <v>-9</v>
@@ -1287,7 +1340,7 @@
       <c r="K7" s="27"/>
       <c r="L7" s="28"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
         <v>16</v>
       </c>
@@ -1300,11 +1353,11 @@
       <c r="D8" s="22">
         <v>25</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
       <c r="H8" s="25"/>
       <c r="I8" s="22">
         <v>-1</v>
@@ -1313,10 +1366,12 @@
         <v>27</v>
       </c>
       <c r="K8" s="27"/>
-      <c r="L8" s="28"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="L8" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="29" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="16" t="s">
@@ -1328,10 +1383,10 @@
       <c r="D9" s="17">
         <v>80</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>2</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="31">
         <v>11</v>
       </c>
       <c r="G9" s="18">
@@ -1346,10 +1401,14 @@
       <c r="J9" s="19">
         <v>80</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="32" customFormat="1">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -1381,9 +1440,11 @@
         <v>26</v>
       </c>
       <c r="K10" s="27"/>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="32" customFormat="1">
       <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
@@ -1396,11 +1457,11 @@
       <c r="D11" s="22">
         <v>50</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="55"/>
       <c r="H11" s="25"/>
       <c r="I11" s="22">
         <v>10</v>
@@ -1409,10 +1470,12 @@
         <v>50</v>
       </c>
       <c r="K11" s="27"/>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="L11" s="28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="33" customFormat="1">
+      <c r="A12" s="29" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="16" t="s">
@@ -1424,10 +1487,10 @@
       <c r="D12" s="17">
         <v>25</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>3</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="31">
         <v>8</v>
       </c>
       <c r="G12" s="18">
@@ -1443,10 +1506,12 @@
         <v>27</v>
       </c>
       <c r="K12" s="14"/>
-      <c r="L12" s="15"/>
-    </row>
-    <row r="13" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="L12" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="33" customFormat="1">
+      <c r="A13" s="29" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -1458,11 +1523,11 @@
       <c r="D13" s="17">
         <v>50</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="60"/>
       <c r="H13" s="18"/>
       <c r="I13" s="17">
         <v>9</v>
@@ -1471,10 +1536,12 @@
         <v>50</v>
       </c>
       <c r="K13" s="14"/>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="L13" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="33" customFormat="1">
+      <c r="A14" s="29" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="16" t="s">
@@ -1486,11 +1553,11 @@
       <c r="D14" s="17">
         <v>49</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="18"/>
       <c r="I14" s="17">
         <v>9</v>
@@ -1501,8 +1568,8 @@
       <c r="K14" s="14"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+    <row r="15" spans="1:12" s="33" customFormat="1">
+      <c r="A15" s="29" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="16" t="s">
@@ -1514,11 +1581,11 @@
       <c r="D15" s="17">
         <v>25</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="60"/>
       <c r="H15" s="18"/>
       <c r="I15" s="17">
         <v>5</v>
@@ -1529,8 +1596,8 @@
       <c r="K15" s="14"/>
       <c r="L15" s="15"/>
     </row>
-    <row r="16" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+    <row r="16" spans="1:12" s="33" customFormat="1">
+      <c r="A16" s="29" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="16" t="s">
@@ -1542,11 +1609,11 @@
       <c r="D16" s="17">
         <v>50</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="60"/>
       <c r="H16" s="18"/>
       <c r="I16" s="17">
         <v>5</v>
@@ -1557,8 +1624,8 @@
       <c r="K16" s="14"/>
       <c r="L16" s="15"/>
     </row>
-    <row r="17" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+    <row r="17" spans="1:12" s="33" customFormat="1">
+      <c r="A17" s="29" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="16" t="s">
@@ -1570,11 +1637,11 @@
       <c r="D17" s="17">
         <v>49</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="60"/>
       <c r="H17" s="18"/>
       <c r="I17" s="17">
         <v>5</v>
@@ -1585,7 +1652,7 @@
       <c r="K17" s="14"/>
       <c r="L17" s="15"/>
     </row>
-    <row r="18" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="32" customFormat="1">
       <c r="A18" s="20" t="s">
         <v>36</v>
       </c>
@@ -1617,9 +1684,11 @@
         <v>28</v>
       </c>
       <c r="K18" s="27"/>
-      <c r="L18" s="28"/>
-    </row>
-    <row r="19" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L18" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="32" customFormat="1">
       <c r="A19" s="20" t="s">
         <v>38</v>
       </c>
@@ -1632,11 +1701,11 @@
       <c r="D19" s="22">
         <v>50</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="51"/>
-      <c r="G19" s="52"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="55"/>
       <c r="H19" s="25"/>
       <c r="I19" s="22">
         <v>4</v>
@@ -1645,9 +1714,11 @@
         <v>50</v>
       </c>
       <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-    </row>
-    <row r="20" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L19" s="28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="32" customFormat="1">
       <c r="A20" s="20" t="s">
         <v>40</v>
       </c>
@@ -1660,11 +1731,11 @@
       <c r="D20" s="22">
         <v>49</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="52"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="55"/>
       <c r="H20" s="25"/>
       <c r="I20" s="22">
         <v>4</v>
@@ -1675,7 +1746,7 @@
       <c r="K20" s="27"/>
       <c r="L20" s="28"/>
     </row>
-    <row r="21" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="32" customFormat="1">
       <c r="A21" s="20" t="s">
         <v>41</v>
       </c>
@@ -1688,11 +1759,11 @@
       <c r="D21" s="22">
         <v>48</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="55"/>
       <c r="H21" s="25"/>
       <c r="I21" s="22">
         <v>4</v>
@@ -1703,7 +1774,7 @@
       <c r="K21" s="27"/>
       <c r="L21" s="28"/>
     </row>
-    <row r="22" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="32" customFormat="1">
       <c r="A22" s="20" t="s">
         <v>42</v>
       </c>
@@ -1716,11 +1787,11 @@
       <c r="D22" s="22">
         <v>25</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="51"/>
-      <c r="G22" s="52"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="55"/>
       <c r="H22" s="25"/>
       <c r="I22" s="22">
         <v>0</v>
@@ -1731,7 +1802,7 @@
       <c r="K22" s="27"/>
       <c r="L22" s="28"/>
     </row>
-    <row r="23" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="32" customFormat="1">
       <c r="A23" s="20" t="s">
         <v>44</v>
       </c>
@@ -1744,11 +1815,11 @@
       <c r="D23" s="22">
         <v>50</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="55"/>
       <c r="H23" s="25"/>
       <c r="I23" s="22">
         <v>0</v>
@@ -1759,7 +1830,7 @@
       <c r="K23" s="27"/>
       <c r="L23" s="28"/>
     </row>
-    <row r="24" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="32" customFormat="1">
       <c r="A24" s="20" t="s">
         <v>45</v>
       </c>
@@ -1772,11 +1843,11 @@
       <c r="D24" s="22">
         <v>49</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="52"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
       <c r="H24" s="25"/>
       <c r="I24" s="22">
         <v>0</v>
@@ -1787,7 +1858,7 @@
       <c r="K24" s="27"/>
       <c r="L24" s="28"/>
     </row>
-    <row r="25" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" s="32" customFormat="1">
       <c r="A25" s="20" t="s">
         <v>46</v>
       </c>
@@ -1800,11 +1871,11 @@
       <c r="D25" s="22">
         <v>48</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="51"/>
-      <c r="G25" s="52"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
       <c r="H25" s="25"/>
       <c r="I25" s="22">
         <v>0</v>
@@ -1815,8 +1886,8 @@
       <c r="K25" s="27"/>
       <c r="L25" s="28"/>
     </row>
-    <row r="26" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+    <row r="26" spans="1:12" s="33" customFormat="1">
+      <c r="A26" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B26" s="16" t="s">
@@ -1828,10 +1899,10 @@
       <c r="D26" s="17">
         <v>25</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <v>3</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="31">
         <v>10</v>
       </c>
       <c r="G26" s="18">
@@ -1847,9 +1918,11 @@
         <v>0</v>
       </c>
       <c r="K26" s="14"/>
-      <c r="L26" s="15"/>
-    </row>
-    <row r="27" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L26" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="32" customFormat="1">
       <c r="A27" s="20" t="s">
         <v>49</v>
       </c>
@@ -1871,7 +1944,7 @@
       <c r="G27" s="25">
         <v>12</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="H27" s="34" t="s">
         <v>50</v>
       </c>
       <c r="I27" s="22">
@@ -1881,10 +1954,12 @@
         <v>0</v>
       </c>
       <c r="K27" s="27"/>
-      <c r="L27" s="28"/>
-    </row>
-    <row r="28" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="L27" s="28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="33" customFormat="1">
+      <c r="A28" s="29" t="s">
         <v>51</v>
       </c>
       <c r="B28" s="16" t="s">
@@ -1896,10 +1971,10 @@
       <c r="D28" s="17">
         <v>20</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="30">
         <v>4</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="31">
         <v>5</v>
       </c>
       <c r="G28" s="18">
@@ -1914,11 +1989,15 @@
       <c r="J28" s="19">
         <v>19</v>
       </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="15"/>
-    </row>
-    <row r="29" spans="1:12" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="K28" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="33" customFormat="1">
+      <c r="A29" s="29" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="16" t="s">
@@ -1930,11 +2009,11 @@
       <c r="D29" s="17">
         <v>0</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="E29" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="60"/>
       <c r="H29" s="18"/>
       <c r="I29" s="17">
         <v>9</v>
@@ -1943,9 +2022,11 @@
         <v>0</v>
       </c>
       <c r="K29" s="14"/>
-      <c r="L29" s="15"/>
-    </row>
-    <row r="30" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L29" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="32" customFormat="1">
       <c r="A30" s="20" t="s">
         <v>55</v>
       </c>
@@ -1967,7 +2048,7 @@
       <c r="G30" s="25">
         <v>12</v>
       </c>
-      <c r="H30" s="35" t="s">
+      <c r="H30" s="34" t="s">
         <v>56</v>
       </c>
       <c r="I30" s="22">
@@ -1977,37 +2058,39 @@
         <v>23</v>
       </c>
       <c r="K30" s="27"/>
-      <c r="L30" s="28"/>
-    </row>
-    <row r="31" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
+      <c r="L30" s="28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="32" customFormat="1">
+      <c r="A31" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="64">
+      <c r="C31" s="43">
         <v>-8</v>
       </c>
-      <c r="D31" s="64">
+      <c r="D31" s="43">
         <v>1</v>
       </c>
-      <c r="E31" s="47" t="s">
+      <c r="E31" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="64">
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="43">
         <v>-9</v>
       </c>
-      <c r="J31" s="65">
+      <c r="J31" s="44">
         <v>0</v>
       </c>
       <c r="K31" s="27"/>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" s="32" customFormat="1">
       <c r="A32" s="20" t="s">
         <v>58</v>
       </c>
@@ -2020,12 +2103,12 @@
       <c r="D32" s="22">
         <v>0</v>
       </c>
-      <c r="E32" s="50" t="s">
+      <c r="E32" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F32" s="51"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="29"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="25"/>
       <c r="I32" s="22">
         <v>-9</v>
       </c>
@@ -2033,43 +2116,50 @@
         <v>0</v>
       </c>
       <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
-    </row>
-    <row r="33" spans="1:12" s="33" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="39" t="s">
+      <c r="L32" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="32" customFormat="1" ht="15" thickBot="1">
+      <c r="A33" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="66">
+      <c r="C33" s="45">
         <v>0</v>
       </c>
-      <c r="D33" s="66">
+      <c r="D33" s="45">
         <v>25</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="54"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="66">
+      <c r="F33" s="65"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="45">
         <v>-1</v>
       </c>
-      <c r="J33" s="67">
+      <c r="J33" s="46">
         <v>23</v>
       </c>
-      <c r="K33" s="43"/>
-      <c r="L33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:G2"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="E4:G4"/>
@@ -2083,16 +2173,11 @@
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="68" orientation="landscape" r:id="rId1"/>
